--- a/data/trans_dic/P16A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 18,58</t>
+          <t>10,2; 19,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 22,15</t>
+          <t>12,62; 21,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 27,1</t>
+          <t>16,72; 26,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,36; 35,86</t>
+          <t>23,55; 35,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,93; 24,0</t>
+          <t>14,02; 23,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 31,51</t>
+          <t>20,76; 31,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 39,79</t>
+          <t>28,13; 39,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,89; 48,81</t>
+          <t>39,12; 48,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,14; 19,47</t>
+          <t>13,13; 19,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 25,09</t>
+          <t>17,9; 25,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,74; 31,41</t>
+          <t>23,47; 31,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 40,2</t>
+          <t>32,72; 40,33</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,42</t>
+          <t>6,94; 12,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 25,08</t>
+          <t>17,64; 24,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 20,55</t>
+          <t>14,13; 20,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,03; 27,54</t>
+          <t>19,19; 27,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 25,83</t>
+          <t>18,92; 25,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,56; 39,13</t>
+          <t>30,73; 38,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 34,35</t>
+          <t>26,03; 34,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,84; 44,82</t>
+          <t>37,04; 44,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,41</t>
+          <t>13,82; 18,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,05; 30,92</t>
+          <t>25,0; 30,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 26,43</t>
+          <t>20,97; 26,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 35,01</t>
+          <t>29,05; 34,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,69</t>
+          <t>7,93; 15,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 26,99</t>
+          <t>17,99; 27,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 24,29</t>
+          <t>15,88; 23,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,1; 33,79</t>
+          <t>23,75; 34,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,33; 34,31</t>
+          <t>24,02; 33,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,99; 37,45</t>
+          <t>27,01; 37,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,15; 38,09</t>
+          <t>27,86; 38,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,67; 46,79</t>
+          <t>37,76; 46,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 23,43</t>
+          <t>17,21; 23,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 30,93</t>
+          <t>23,77; 31,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 30,02</t>
+          <t>23,29; 29,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,6; 39,06</t>
+          <t>32,36; 39,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 18,67</t>
+          <t>11,85; 19,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 24,47</t>
+          <t>15,4; 24,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 33,44</t>
+          <t>23,94; 33,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 37,37</t>
+          <t>24,7; 37,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 26,86</t>
+          <t>18,34; 27,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,21; 46,49</t>
+          <t>35,74; 45,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,98; 51,25</t>
+          <t>40,59; 50,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 44,22</t>
+          <t>20,36; 44,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 21,73</t>
+          <t>15,98; 21,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 33,66</t>
+          <t>27,18; 33,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,75; 40,73</t>
+          <t>33,75; 40,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,71; 38,7</t>
+          <t>23,77; 38,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 19,51</t>
+          <t>9,93; 19,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,8; 22,59</t>
+          <t>12,14; 22,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,78</t>
+          <t>9,66; 19,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 28,64</t>
+          <t>18,15; 28,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 31,86</t>
+          <t>19,4; 31,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,53; 50,77</t>
+          <t>37,92; 51,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 35,61</t>
+          <t>24,18; 35,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 43,9</t>
+          <t>34,95; 43,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 23,85</t>
+          <t>15,92; 24,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,72; 36,12</t>
+          <t>26,4; 35,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 25,92</t>
+          <t>18,54; 26,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,81; 35,73</t>
+          <t>28,52; 35,2</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,95; 17,66</t>
+          <t>9,8; 17,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,07; 24,5</t>
+          <t>14,87; 24,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,06</t>
+          <t>10,63; 19,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,94; 34,4</t>
+          <t>24,64; 34,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 30,17</t>
+          <t>20,04; 29,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,24; 43,17</t>
+          <t>31,86; 44,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,22; 31,0</t>
+          <t>20,0; 31,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,27; 48,09</t>
+          <t>38,17; 48,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,17; 22,43</t>
+          <t>15,86; 22,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,16; 32,83</t>
+          <t>25,19; 32,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,9; 23,96</t>
+          <t>16,83; 24,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,37; 39,34</t>
+          <t>32,49; 39,6</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,29</t>
+          <t>11,23; 16,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 19,98</t>
+          <t>14,05; 20,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,2</t>
+          <t>12,39; 17,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 31,18</t>
+          <t>22,84; 31,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,66; 23,84</t>
+          <t>17,62; 24,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,81; 35,78</t>
+          <t>28,79; 35,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,84; 25,29</t>
+          <t>19,11; 25,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,75; 75,72</t>
+          <t>39,65; 77,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 19,87</t>
+          <t>15,5; 19,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,32; 27,01</t>
+          <t>22,46; 27,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 20,69</t>
+          <t>16,52; 21,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,28; 65,76</t>
+          <t>32,86; 63,65</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,04; 20,77</t>
+          <t>14,83; 20,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 17,12</t>
+          <t>11,83; 17,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,11; 22,87</t>
+          <t>17,37; 23,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 14,64</t>
+          <t>5,03; 14,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,59; 30,38</t>
+          <t>24,11; 30,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,84; 32,48</t>
+          <t>25,91; 32,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 36,55</t>
+          <t>30,14; 36,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 34,2</t>
+          <t>28,26; 34,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,61; 24,81</t>
+          <t>20,49; 24,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,64; 24,01</t>
+          <t>19,86; 24,19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,48; 29,3</t>
+          <t>24,58; 29,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 23,27</t>
+          <t>11,56; 23,26</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,8; 15,25</t>
+          <t>12,82; 15,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,55; 19,24</t>
+          <t>16,51; 19,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,67; 20,21</t>
+          <t>17,57; 20,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,4; 24,74</t>
+          <t>17,53; 24,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,42</t>
+          <t>22,43; 25,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,8; 35,15</t>
+          <t>31,96; 35,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,45; 32,61</t>
+          <t>29,51; 32,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,91; 53,16</t>
+          <t>37,63; 51,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,95</t>
+          <t>17,99; 19,95</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,79; 26,98</t>
+          <t>24,81; 27,02</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,02; 26,25</t>
+          <t>24,12; 26,36</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,14; 39,03</t>
+          <t>29,35; 38,79</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27159; 50720</t>
+          <t>27847; 51906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37072; 64712</t>
+          <t>36868; 63731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49533; 79621</t>
+          <t>49110; 78087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72757; 111689</t>
+          <t>73330; 111069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36327; 62603</t>
+          <t>36560; 61871</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59658; 89471</t>
+          <t>58964; 89554</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81125; 114866</t>
+          <t>81202; 114513</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>112647; 141372</t>
+          <t>113308; 141176</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70168; 103942</t>
+          <t>70118; 102532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102467; 144586</t>
+          <t>103136; 145189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138277; 182946</t>
+          <t>136679; 182161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>193715; 241604</t>
+          <t>196644; 242434</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34557; 61241</t>
+          <t>34206; 60598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89845; 126785</t>
+          <t>89183; 126068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69565; 103304</t>
+          <t>71023; 104076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98673; 142780</t>
+          <t>99499; 143140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94783; 130194</t>
+          <t>95327; 130379</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>159743; 204529</t>
+          <t>160619; 203813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136749; 179668</t>
+          <t>136184; 178078</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189453; 230515</t>
+          <t>190479; 229325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137495; 183565</t>
+          <t>137789; 182319</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257622; 317945</t>
+          <t>257106; 317915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215570; 271109</t>
+          <t>215081; 270119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>299479; 361560</t>
+          <t>299982; 360735</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23919; 46844</t>
+          <t>25284; 48812</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57324; 87220</t>
+          <t>58135; 88334</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49791; 77389</t>
+          <t>50585; 76025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76154; 106793</t>
+          <t>75048; 108279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81609; 115066</t>
+          <t>80564; 113369</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92030; 127728</t>
+          <t>92127; 128570</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94659; 128090</t>
+          <t>93686; 129519</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>131504; 163371</t>
+          <t>131834; 162489</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112093; 153313</t>
+          <t>112602; 153029</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158458; 205440</t>
+          <t>157886; 206079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151847; 196607</t>
+          <t>152535; 195234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>216871; 259852</t>
+          <t>215252; 261360</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40683; 66956</t>
+          <t>42515; 68219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58168; 91519</t>
+          <t>57593; 91562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88599; 123702</t>
+          <t>88552; 123449</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76340; 116789</t>
+          <t>77197; 117054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68726; 99774</t>
+          <t>68142; 100881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>140485; 180370</t>
+          <t>138668; 176540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>158702; 198478</t>
+          <t>157214; 196745</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97535; 210352</t>
+          <t>96874; 211222</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117163; 158692</t>
+          <t>116694; 159498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>204545; 256438</t>
+          <t>207075; 258288</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>255554; 308406</t>
+          <t>255559; 308568</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>194780; 305072</t>
+          <t>187397; 303586</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20328; 39661</t>
+          <t>20198; 40041</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25089; 48039</t>
+          <t>25817; 48007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19885; 39670</t>
+          <t>20402; 41623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33067; 51199</t>
+          <t>32447; 50389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>39552; 66169</t>
+          <t>40292; 65439</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82415; 111495</t>
+          <t>83260; 113733</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51763; 77839</t>
+          <t>52862; 78563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72153; 91600</t>
+          <t>72923; 91156</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66110; 98032</t>
+          <t>65446; 98752</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115499; 156099</t>
+          <t>114083; 155183</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79142; 111398</t>
+          <t>79701; 113522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>111599; 138426</t>
+          <t>110468; 136381</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26959; 47821</t>
+          <t>26543; 48147</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41299; 67119</t>
+          <t>40738; 66547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28492; 52791</t>
+          <t>27979; 51606</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67256; 92751</t>
+          <t>66436; 92916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54729; 83917</t>
+          <t>55733; 82758</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>90009; 120500</t>
+          <t>88937; 122950</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55224; 84661</t>
+          <t>54632; 85015</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>98382; 123621</t>
+          <t>98110; 124023</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>88768; 123121</t>
+          <t>87080; 123815</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139173; 181575</t>
+          <t>139312; 180351</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90627; 128458</t>
+          <t>90240; 130585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>170493; 207181</t>
+          <t>171117; 208596</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>72200; 106342</t>
+          <t>69097; 103771</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90997; 132446</t>
+          <t>93126; 137042</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80125; 119526</t>
+          <t>81334; 116342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>141552; 194636</t>
+          <t>142589; 195380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>112687; 152146</t>
+          <t>112440; 156425</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>199877; 248255</t>
+          <t>199740; 249451</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130208; 174829</t>
+          <t>132114; 176017</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>337568; 643041</t>
+          <t>336773; 659247</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>194416; 248974</t>
+          <t>194216; 248456</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>302736; 366369</t>
+          <t>304721; 371436</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221112; 278831</t>
+          <t>222684; 283508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>490442; 969026</t>
+          <t>484184; 937984</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>111704; 154305</t>
+          <t>110165; 151505</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>92515; 133011</t>
+          <t>91910; 132566</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133234; 178042</t>
+          <t>135273; 181448</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41313; 135955</t>
+          <t>46720; 136839</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>184831; 238065</t>
+          <t>188930; 238819</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>212604; 267211</t>
+          <t>213168; 266891</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>247524; 301940</t>
+          <t>249031; 302704</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>202032; 244463</t>
+          <t>202028; 244886</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>314526; 378642</t>
+          <t>312675; 378531</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>314144; 384069</t>
+          <t>317768; 386917</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>392860; 470252</t>
+          <t>394379; 467581</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>199850; 382436</t>
+          <t>190024; 382352</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>419332; 499643</t>
+          <t>419788; 494030</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>566113; 658389</t>
+          <t>564915; 663418</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599790; 685922</t>
+          <t>596489; 685443</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>602104; 855818</t>
+          <t>606557; 862316</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>760960; 859025</t>
+          <t>758119; 857376</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1129279; 1248204</t>
+          <t>1134909; 1247662</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1043727; 1156043</t>
+          <t>1045830; 1162104</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1387080; 1944977</t>
+          <t>1376601; 1886597</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1199751; 1327515</t>
+          <t>1197256; 1327501</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1728497; 1880953</t>
+          <t>1729485; 1884212</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1666980; 1821371</t>
+          <t>1673737; 1828832</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2074461; 2778298</t>
+          <t>2089193; 2761143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,01</t>
+          <t>9,86; 18,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 21,81</t>
+          <t>12,47; 21,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 26,58</t>
+          <t>17,05; 26,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,55; 35,66</t>
+          <t>25,1; 35,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 23,72</t>
+          <t>13,82; 23,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 31,54</t>
+          <t>20,94; 31,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 39,66</t>
+          <t>27,74; 39,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,12; 48,74</t>
+          <t>38,55; 47,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 19,21</t>
+          <t>12,93; 19,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 25,2</t>
+          <t>18,09; 25,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 31,27</t>
+          <t>23,66; 31,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,33</t>
+          <t>32,83; 39,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,29</t>
+          <t>7,12; 12,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 24,94</t>
+          <t>17,52; 24,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,13; 20,71</t>
+          <t>14,08; 20,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 27,61</t>
+          <t>19,53; 28,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 25,87</t>
+          <t>19,17; 25,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,73; 38,99</t>
+          <t>30,26; 39,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 34,04</t>
+          <t>26,3; 34,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 44,59</t>
+          <t>36,52; 43,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 18,29</t>
+          <t>13,75; 18,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,0; 30,92</t>
+          <t>25,22; 31,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,34</t>
+          <t>20,73; 26,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 34,93</t>
+          <t>28,98; 35,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,31</t>
+          <t>7,85; 14,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,34</t>
+          <t>17,43; 27,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 23,86</t>
+          <t>15,56; 23,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,75; 34,26</t>
+          <t>24,63; 34,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,02; 33,8</t>
+          <t>24,04; 34,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,01; 37,7</t>
+          <t>27,54; 37,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,86; 38,51</t>
+          <t>27,94; 38,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,76; 46,54</t>
+          <t>38,5; 47,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 23,39</t>
+          <t>16,86; 23,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,77; 31,03</t>
+          <t>24,03; 30,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,29; 29,81</t>
+          <t>23,3; 29,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,36; 39,29</t>
+          <t>33,18; 39,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 19,02</t>
+          <t>11,29; 18,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,4; 24,48</t>
+          <t>15,33; 24,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,94; 33,37</t>
+          <t>23,86; 33,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,7; 37,45</t>
+          <t>23,21; 35,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 27,16</t>
+          <t>18,68; 26,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,74; 45,5</t>
+          <t>35,88; 45,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,59; 50,8</t>
+          <t>40,59; 51,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 44,4</t>
+          <t>39,23; 48,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 21,85</t>
+          <t>16,07; 21,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,18; 33,9</t>
+          <t>26,56; 33,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,75; 40,75</t>
+          <t>33,89; 41,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,77; 38,51</t>
+          <t>33,21; 41,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 19,69</t>
+          <t>10,08; 19,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 22,58</t>
+          <t>12,19; 22,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,71</t>
+          <t>9,4; 18,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 28,19</t>
+          <t>16,97; 26,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 31,51</t>
+          <t>19,37; 32,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,92; 51,79</t>
+          <t>37,73; 51,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 35,94</t>
+          <t>23,68; 36,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,95; 43,69</t>
+          <t>33,33; 42,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 24,03</t>
+          <t>16,05; 23,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 35,9</t>
+          <t>26,5; 35,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 26,41</t>
+          <t>18,03; 25,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,52; 35,2</t>
+          <t>27,22; 33,27</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,8; 17,78</t>
+          <t>9,77; 18,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,87; 24,29</t>
+          <t>15,03; 24,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,61</t>
+          <t>11,2; 19,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,64; 34,46</t>
+          <t>23,84; 33,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,04; 29,75</t>
+          <t>19,82; 29,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,86; 44,05</t>
+          <t>31,61; 43,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,0; 31,13</t>
+          <t>20,43; 31,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,17; 48,25</t>
+          <t>37,91; 48,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,86; 22,55</t>
+          <t>15,96; 22,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,19; 32,61</t>
+          <t>24,92; 33,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,35</t>
+          <t>16,98; 24,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,49; 39,6</t>
+          <t>32,16; 38,81</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 16,87</t>
+          <t>11,45; 17,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 20,68</t>
+          <t>14,01; 20,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,72</t>
+          <t>12,09; 17,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,84; 31,3</t>
+          <t>23,04; 30,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 24,51</t>
+          <t>17,58; 24,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,79; 35,95</t>
+          <t>28,69; 35,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 25,46</t>
+          <t>18,93; 25,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,65; 77,63</t>
+          <t>37,24; 43,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,5; 19,82</t>
+          <t>15,43; 19,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,38</t>
+          <t>22,39; 27,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 21,03</t>
+          <t>16,47; 20,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,86; 63,65</t>
+          <t>31,52; 36,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,83; 20,4</t>
+          <t>15,23; 20,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,06</t>
+          <t>11,79; 17,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,3</t>
+          <t>17,4; 23,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 14,73</t>
+          <t>11,05; 15,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,11; 30,48</t>
+          <t>23,85; 30,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,91; 32,44</t>
+          <t>25,86; 32,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,14; 36,64</t>
+          <t>29,93; 36,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 34,26</t>
+          <t>27,55; 33,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 24,8</t>
+          <t>20,52; 24,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,19</t>
+          <t>19,82; 24,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,58; 29,14</t>
+          <t>24,46; 29,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,26</t>
+          <t>20,14; 23,86</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,82; 15,08</t>
+          <t>12,79; 15,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,39</t>
+          <t>16,42; 19,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,19</t>
+          <t>17,53; 20,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,92</t>
+          <t>22,26; 25,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,37</t>
+          <t>22,27; 25,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,96; 35,14</t>
+          <t>31,8; 35,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,51; 32,79</t>
+          <t>29,64; 32,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,63; 51,57</t>
+          <t>37,54; 40,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,95</t>
+          <t>17,95; 19,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,81; 27,02</t>
+          <t>24,74; 26,97</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,12; 26,36</t>
+          <t>24,12; 26,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,35; 38,79</t>
+          <t>30,63; 32,62</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>95102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>136010</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>218255</t>
+          <t>231112</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27847; 51906</t>
+          <t>26907; 50912</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36868; 63731</t>
+          <t>36444; 63570</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49110; 78087</t>
+          <t>50100; 78659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73330; 111069</t>
+          <t>80038; 113700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36560; 61871</t>
+          <t>36057; 61249</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58964; 89554</t>
+          <t>59465; 89995</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81202; 114513</t>
+          <t>80081; 112974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113308; 141176</t>
+          <t>121828; 149694</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70118; 102532</t>
+          <t>69015; 102406</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103136; 145189</t>
+          <t>104246; 145417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136679; 182161</t>
+          <t>137801; 183206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>196644; 242434</t>
+          <t>208463; 253714</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119718</t>
+          <t>123088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>209328</t>
+          <t>218316</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>329046</t>
+          <t>341404</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34206; 60598</t>
+          <t>35123; 62487</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89183; 126068</t>
+          <t>88569; 126051</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71023; 104076</t>
+          <t>70764; 105010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99499; 143140</t>
+          <t>103620; 149104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95327; 130379</t>
+          <t>96583; 130753</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160619; 203813</t>
+          <t>158180; 204584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136184; 178078</t>
+          <t>137549; 180284</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>190479; 229325</t>
+          <t>199311; 239338</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137789; 182319</t>
+          <t>137067; 181959</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257106; 317915</t>
+          <t>259353; 319147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215081; 270119</t>
+          <t>212616; 271216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>299982; 360735</t>
+          <t>311998; 378114</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>92500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>146969</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>237434</t>
+          <t>244717</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25284; 48812</t>
+          <t>25039; 47257</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58135; 88334</t>
+          <t>56308; 87489</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50585; 76025</t>
+          <t>49574; 75776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75048; 108279</t>
+          <t>77830; 109690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80564; 113369</t>
+          <t>80629; 114248</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92127; 128570</t>
+          <t>93916; 129368</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93686; 129519</t>
+          <t>93955; 129772</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>131834; 162489</t>
+          <t>137222; 168382</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112602; 153029</t>
+          <t>110308; 151751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157886; 206079</t>
+          <t>159592; 205679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152535; 195234</t>
+          <t>152600; 195955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>215252; 261360</t>
+          <t>223067; 267159</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>166330</t>
+          <t>183414</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>261478</t>
+          <t>293062</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42515; 68219</t>
+          <t>40479; 66624</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57593; 91562</t>
+          <t>57314; 91979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88552; 123449</t>
+          <t>88290; 123234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77197; 117054</t>
+          <t>86621; 133147</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68142; 100881</t>
+          <t>69373; 99980</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>138668; 176540</t>
+          <t>139209; 176733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157214; 196745</t>
+          <t>157216; 198427</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96874; 211222</t>
+          <t>165531; 203523</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116694; 159498</t>
+          <t>117352; 158616</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>207075; 258288</t>
+          <t>202409; 257627</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>255559; 308568</t>
+          <t>256605; 311558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>187397; 303586</t>
+          <t>264057; 326018</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>123408</t>
+          <t>130282</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20198; 40041</t>
+          <t>20503; 39711</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25817; 48007</t>
+          <t>25925; 48806</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20402; 41623</t>
+          <t>19847; 39318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32447; 50389</t>
+          <t>34895; 54615</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40292; 65439</t>
+          <t>40217; 66943</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83260; 113733</t>
+          <t>82855; 113610</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52862; 78563</t>
+          <t>51756; 78998</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72923; 91156</t>
+          <t>75730; 96430</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65446; 98752</t>
+          <t>65944; 98332</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114083; 155183</t>
+          <t>114534; 154971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79701; 113522</t>
+          <t>77499; 111086</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>110468; 136381</t>
+          <t>117831; 144038</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78873</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>189408</t>
+          <t>190174</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26543; 48147</t>
+          <t>26445; 49057</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40738; 66547</t>
+          <t>41192; 68398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27979; 51606</t>
+          <t>29464; 52502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66436; 92916</t>
+          <t>64544; 89555</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55733; 82758</t>
+          <t>55141; 83244</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88937; 122950</t>
+          <t>88225; 121947</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54632; 85015</t>
+          <t>55807; 84774</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>98110; 124023</t>
+          <t>99989; 126894</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87080; 123815</t>
+          <t>87593; 124244</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139312; 180351</t>
+          <t>137833; 183453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90240; 130585</t>
+          <t>91036; 129923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>171117; 208596</t>
+          <t>171874; 207406</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166105</t>
+          <t>191537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>469240</t>
+          <t>314274</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>635345</t>
+          <t>505812</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>69097; 103771</t>
+          <t>70415; 104961</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>93126; 137042</t>
+          <t>92828; 133847</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81334; 116342</t>
+          <t>79391; 118007</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142589; 195380</t>
+          <t>165781; 220928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>112440; 156425</t>
+          <t>112195; 156012</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>199740; 249451</t>
+          <t>199041; 249419</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>132114; 176017</t>
+          <t>130881; 176408</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>336773; 659247</t>
+          <t>287539; 337458</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>194216; 248456</t>
+          <t>193405; 249405</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>304721; 371436</t>
+          <t>303729; 368765</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222684; 283508</t>
+          <t>222037; 281028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>484184; 937984</t>
+          <t>470137; 543088</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94263</t>
+          <t>105836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>222539</t>
+          <t>251438</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>316802</t>
+          <t>357274</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>110165; 151505</t>
+          <t>113122; 152006</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91910; 132566</t>
+          <t>91627; 132256</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>135273; 181448</t>
+          <t>135471; 181882</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46720; 136839</t>
+          <t>88214; 127404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>188930; 238819</t>
+          <t>186877; 238570</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>213168; 266891</t>
+          <t>212738; 266932</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>249031; 302704</t>
+          <t>247266; 304954</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>202028; 244886</t>
+          <t>228664; 274617</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>312675; 378531</t>
+          <t>313216; 378149</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>317768; 386917</t>
+          <t>317050; 387149</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>394379; 467581</t>
+          <t>392589; 467645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>190024; 382352</t>
+          <t>327965; 388500</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>419788; 494030</t>
+          <t>418796; 496828</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>564915; 663418</t>
+          <t>561679; 661042</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>596489; 685443</t>
+          <t>595150; 688038</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>606557; 862316</t>
+          <t>786469; 898424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>758119; 857376</t>
+          <t>752583; 853098</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1134909; 1247662</t>
+          <t>1129220; 1246793</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1045830; 1162104</t>
+          <t>1050441; 1161428</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1376601; 1886597</t>
+          <t>1401329; 1502432</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1197256; 1327501</t>
+          <t>1194525; 1326086</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1729485; 1884212</t>
+          <t>1725197; 1880104</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1673737; 1828832</t>
+          <t>1673551; 1815264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2089193; 2761143</t>
+          <t>2225276; 2370307</t>
         </is>
       </c>
     </row>
